--- a/www/flightdata/xlsx/eoss-353.xlsx
+++ b/www/flightdata/xlsx/eoss-353.xlsx
@@ -2514,7 +2514,7 @@
         <v>22073.92</v>
       </c>
       <c r="I2">
-        <v>435</v>
+        <v>282</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
